--- a/mapping/mapping_workbook.xlsx
+++ b/mapping/mapping_workbook.xlsx
@@ -13,15 +13,17 @@
     <sheet name="Asana to ServiceNow" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Adaptive to ServiceNow" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="ServiceNow Form Fields" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Value Maps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Transform Maps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Value Maps" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Data Quality'!$A$1:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Data Quality'!$A$1:$H$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Asana to ServiceNow'!$A$1:$N$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Adaptive to ServiceNow'!$A$1:$N$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'ServiceNow Form Fields'!$A$1:$I$79</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Value Maps'!$A$1:$E$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Transform Maps'!$A$1:$L$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Value Maps'!$A$1:$E$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -520,6 +522,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   'Transform Maps' is the build sheet for the import set transform maps: one row per field map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>6. Copy agreed changes back into the CSVs (the CSVs are the source of truth for the code).</t>
         </is>
@@ -536,17 +545,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,17 +655,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>How should the 18 Asana sections (HR COE areas) and the HR tracker land?</t>
+          <t>Asana task mapping says COE -&gt; parent.portfolio. Sections (COE areas) therefore become portfolios.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(a) Portfolio 'Human Resources' + one program per section (b) portfolio only; section in description (c) section -&gt; department</t>
+          <t>(a) one portfolio per section (18) (b) consolidate small sections (c) HR portfolio + programs per section</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(a) HR portfolio + programs per section; merge single-item sections (Risk Mitigation; PCC/HR Committee) into a neighbour</t>
+          <t>(a) as you mapped, but merge the single-project sections (Risk Mitigation; PCC/HR Committee meetings; HR Services) and treat Ireland Projects / Nursing Projects / GBS Initiatives as programs if they are really programs</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Decided (COE -&gt; portfolio) - consolidation open</t>
         </is>
       </c>
     </row>
@@ -1255,10 +1264,132 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Entity/Organization -&gt; Business Category</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Your task mapping sends Entity/Organization (BSMH, RSFH, GBS, External Partners) to u_business_category. Only RSFH exists on the category list; on current data 44 of 73 HR projects get no category and joint BSMH+RSFH projects become 'rsfh'.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>(a) keep as mapped and add BSMH (and GBS) to the category list (b) Entity -&gt; business_unit / impacted business units only; HR projects get a 'Human Resources' category (c) keep as mapped</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>(b) Entity is an organization, not a work category - it already loads into business_unit and impacted_business_units. Add 'Human Resources' to the unified category list (D1)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Most HR projects load with a blank Business Category</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HR PMO + SN platform owner</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>u_sites field type</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>u_sites is typed 'list' on the form. Does it reference a table (cmn_location or a custom Sites table) or hold choice values?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(a) reference list -&gt; transform script resolves names to sys_ids (b) choice-based list -&gt; load comma-separated values</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Confirm in sys_dictionary (reference column on the u_sites entry). The transform-map script assumes (a)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sites load blank</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SN platform owner</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Load mechanism</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>How does data get into ServiceNow?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>(a) CSV files -&gt; import set -&gt; transform map (b) same, pushed through the Import Set REST API (c) IntegrationHub spokes / middleware</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>(a) for mock 1; (a) via a reusable Data Source or (b) for mocks 2-3 and cutover. No IntegrationHub or live connection between the tools is needed for a one-time migration (docs/08)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Migration lead</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Decided (import set + transform map)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H20"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H216" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H219" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Proposed,Confirmed,Deferred,Not migrating,Open question,Open,Fixed in code,Fixed in config,Partly fixed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1272,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2041,10 +2172,94 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DQ19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Updated form workbooks show no new custom fields</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ServiceNow_Project_Form_Fields.xlsx and Project_Form_Fields_1.xlsx (23 Sep) have the same cells as the 16 Sep version; custom fields are still u_business_owner, u_executive_sponsor, u_cn, u_funding_type, u_funding_source, u_business_category, u_sites (+ u_demand_type on demand)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>The 11 proposed fields (u_legacy_id, lifecycle dates, u_cost_center, u_risk_health ...) are not confirmed as created</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Send the updated workbook or a sys_dictionary export filtered to name STARTSWITH u_ on task, pm_project, dmn_demand, project_status</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ServiceNow export</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DQ20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Asana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Task-level COE and Entity vary within one plan</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Template plan: tasks carry Benefits, Compensation and Learning COEs; mapping sends COE to the parent's single portfolio</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Portfolio depends on which tasks were tagged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Project-level section wins; task COE only fills blanks; disagreements listed in rollup_conflicts.csv</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pipeline (done)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Fixed in code</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H20"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H217" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H219" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Proposed,Confirmed,Deferred,Not migrating,Open question,Open,Fixed in code,Fixed in config,Partly fixed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2067,11 +2282,11 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
+    <col width="43" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2238,32 +2453,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>primary_program</t>
+          <t>primary_portfolio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Portfolio</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Section name -&gt; pm_program.name</t>
+          <t>Section (COE area) -&gt; pm_portfolio.name; task-level COE fills it when the item has no section</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>program_name</t>
+          <t>portfolio_name</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Map (create 18 HR programs)</t>
+          <t>Map (per your task mapping: COE -&gt; parent.portfolio)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Open question</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2273,7 +2488,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Sections are HR COE areas. Alternative: department or a COE field. Also appended to description</t>
+          <t>Creates 18 portfolios on current data (several with 1 project) - consider consolidating. Appended to description too</t>
         </is>
       </c>
     </row>
@@ -3410,40 +3625,44 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>business_unit + impacted_business_units</t>
+          <t>u_business_category (+ business_unit, impacted_business_units)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Business Unit / Impacted Business Units</t>
+          <t>Business Category / Business Unit</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>First value -&gt; business_unit; all -&gt; impacted list</t>
+          <t>First mappable value -&gt; u_business_category (RSFH -&gt; rsfh); first value -&gt; business_unit; all -&gt; impacted list</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>business_unit</t>
+          <t>business_category_project / business_unit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>Map (per your task mapping) - see D17</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Open question</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>On current data 44 of 73 projects get no category (BSMH/GBS/External Partners have no choice value)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3815,7 +4034,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3870,18 +4089,18 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>Map as phase tasks (your mapping left Section blank)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Open question</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Matches a phase-based project template - consider building it in ServiceNow</t>
+          <t>Keeps the Initiation/Build/Test... structure. Alternative: drop sections and load tasks flat</t>
         </is>
       </c>
     </row>
@@ -3913,35 +4132,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>pm_project_task</t>
+          <t>pm_project</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>description (append)</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>primary_portfolio (parent)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Drop or append</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>Roll up: most common task COE fills the project's portfolio if it has none</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>portfolio_name</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Do not migrate</t>
+          <t>Map (your mapping: COE -&gt; parent.portfolio)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Project-level COEs already captured</t>
+          <t>Tasks in one plan carry different COEs (Benefits/Compensation/Learning) - disagreements go to rollup_conflicts.csv</t>
         </is>
       </c>
     </row>
@@ -3995,7 +4226,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4059,7 +4290,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -4115,7 +4346,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -4179,7 +4410,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -4239,11 +4470,15 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Your mapping: percent_complete (number). 0.5 -&gt; 50</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4399,7 +4634,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -4493,27 +4728,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>pm_project_task</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>u_business_category (parent)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Business Category</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Roll up: most common task Entity fills the project's category if it has none</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>business_category_project</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Do not migrate</t>
+          <t>Map (your mapping: Entity/Organization -&gt; parent.u_business_category)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+          <t>Open question</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Project-level only in ServiceNow</t>
+          <t>Only RSFH has a matching category value</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4826,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -10061,7 +10316,5158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:L107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>import_set_table</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>load_file</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>source_column</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>target_table</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>target_field</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>field_kind</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>coalesce</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>referenced_value_field</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>choice_action</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>target_field_status</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>u_correlation_id</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>correlation_id</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Coalesce key - re-loads update instead of duplicating</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>u_correlation_display</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>correlation_display</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>u_u_legacy_id</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>u_legacy_id</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>u_u_legacy_url</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>u_legacy_url</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>u_short_description</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>short_description</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>u_description</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>u_type</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Values from value map 'constant' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>u_u_demand_type</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>u_demand_type</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Values from value map 'demand_type' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>u_category</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Values from value map 'demand_category' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>u_state</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Values from value map 'demand_state' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>u_assigned_to</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>assigned_to</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Reference sys_user</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Never 'create' - it would create users</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>u_opened_by</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>opened_by</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Reference sys_user</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Never 'create' - it would create users</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>u_u_business_owner</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>u_business_owner</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reference sys_user</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Never 'create' - it would create users</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>u_u_executive_sponsor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>u_executive_sponsor</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Reference sys_user</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Never 'create' - it would create users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>u_portfolio</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>portfolio</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Reference pm_portfolio</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>reject (mock loads) / ignore (final)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Records must exist before the load</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>u_primary_program</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>primary_program</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Reference pm_program</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>reject (mock loads) / ignore (final)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Records must exist before the load</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>u_u_cn</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>u_cn</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>u_u_funding_type</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>u_funding_type</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Values from value map 'funding_type' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>u_u_funding_source</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>u_funding_source</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>u_expense_type</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>expense_type</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Values from value map 'expense_type' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>u_u_business_category</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>u_business_category</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Values from value map 'business_category_demand' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>u_u_sites</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>u_sites</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>split names -&gt; sys_ids of the referenced table</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>docs/05 section 4 (list fields). Confirm what u_sites references (D18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>u_business_unit</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>business_unit</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Reference business_unit</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>reject (mock loads) / ignore (final)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Records must exist before the load</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>u_impacted_business_units</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>impacted_business_units</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>split names -&gt; sys_ids of the referenced table</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>docs/05 section 4 (list fields). Confirm what u_sites references (D18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>u_u_cost_center</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>u_cost_center</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Reference cmn_cost_center</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>u_size</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Values from value map 'tshirt_size' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>u_start_date</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>u_due_date</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>due_date</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>u_priority</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Values from value map 'priority' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>u_business_case</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>business_case</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>u_u_request_received</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>u_request_received</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>u_u_request_assigned</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>u_request_assigned</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>u_u_estimate_complete</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>u_estimate_complete</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>u_imp_spm_demand</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>01_dmn_demand.csv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>u_u_estimate_type</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>dmn_demand</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>u_estimate_type</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Values from value map 'estimate_type' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>u_correlation_id</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>correlation_id</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Coalesce key - re-loads update instead of duplicating</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>u_correlation_display</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>correlation_display</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>u_u_legacy_id</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>u_legacy_id</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>u_u_legacy_url</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>u_legacy_url</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>u_short_description</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>short_description</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>u_description</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>u_project_manager</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>project_manager</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Reference sys_user</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Never 'create' - it would create users</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>u_u_business_owner</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>u_business_owner</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Reference sys_user</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Never 'create' - it would create users</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>u_u_executive_sponsor</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>u_executive_sponsor</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Reference sys_user</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Never 'create' - it would create users</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>u_state</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Values from value map 'project_state' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>u_phase</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Values from value map 'project_phase' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>u_start_date</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>u_end_date</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>u_work_start</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>work_start</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>u_work_end</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>work_end</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>u_percent_complete</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>percent_complete</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>u_primary_portfolio</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>primary_portfolio</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Reference pm_portfolio</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>reject (mock loads) / ignore (final)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Records must exist before the load</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>u_primary_program</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>primary_program</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Reference pm_program</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>reject (mock loads) / ignore (final)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Records must exist before the load</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>u_investment_class</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>investment_class</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Values from value map 'investment_class' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>u_u_cn</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>u_cn</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>u_u_funding_type</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>u_funding_type</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Values from value map 'funding_type' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>u_u_funding_source</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>u_funding_source</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>u_expense_type</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>expense_type</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Values from value map 'expense_type' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>u_u_business_category</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>u_business_category</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Values from value map 'business_category_project' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>u_u_sites</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>u_sites</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>split names -&gt; sys_ids of the referenced table</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>exists (custom)</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>docs/05 section 4 (list fields). Confirm what u_sites references (D18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>u_business_unit</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>business_unit</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Reference business_unit</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>reject (mock loads) / ignore (final)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Records must exist before the load</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>u_impacted_business_units</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>impacted_business_units</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>split names -&gt; sys_ids of the referenced table</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>docs/05 section 4 (list fields). Confirm what u_sites references (D18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>u_u_cost_center</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>u_cost_center</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Reference cmn_cost_center</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>u_priority</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Values from value map 'priority' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>u_time_constraint</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>time_constraint</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Values from value map 'constant' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>u_u_next_go_live_date</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>u_next_go_live_date</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>u_u_estimate_type</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>u_estimate_type</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Values from value map 'estimate_type' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>u_u_request_received</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>u_request_received</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>u_u_request_assigned</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>u_request_assigned</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>u_u_estimate_complete</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>u_estimate_complete</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>u_u_ready_for_delivery</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>u_ready_for_delivery</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>u_u_project_assigned</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>u_project_assigned</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>u_u_demand_correlation_id</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>helper - no field map</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Read by the onBefore script (docs/05 section 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>u_imp_spm_project</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>02_pm_project.csv</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>u_u_include_tasks</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>pm_project</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>helper - no field map</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Read by the onBefore script (docs/05 section 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>u_correlation_id</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>correlation_id</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Coalesce key - re-loads update instead of duplicating</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>u_correlation_display</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>correlation_display</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>u_u_legacy_id</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>u_legacy_id</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>u_u_legacy_url</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>u_legacy_url</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>u_u_project_correlation_id</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>helper - no field map</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Read by the onBefore script (docs/05 section 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>u_u_parent_correlation_id</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>helper - no field map</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Read by the onBefore script (docs/05 section 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>u_u_level</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Helper</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>helper - no field map</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Read by the onBefore script (docs/05 section 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>u_wbs_order</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>wbs_order</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>u_short_description</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>short_description</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>u_description</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>u_assigned_to</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>assigned_to</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Reference sys_user</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ignore</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Never 'create' - it would create users</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>u_additional_assignee_list</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>additional_assignee_list</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>List of sys_user</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>split emails -&gt; SPMMigrationUtil.userByEmail()</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>docs/05 section 4 (list fields)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>u_state</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Values from value map 'task_state' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>u_milestone</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>u_start_date</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>u_end_date</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>u_work_start</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>work_start</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>u_work_end</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>work_end</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>u_percent_complete</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>percent_complete</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>u_imp_spm_task</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>03_pm_project_task.csv</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>u_time_constraint</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>pm_project_task</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>time_constraint</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Values from value map 'constant' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>u_imp_spm_dependency</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>04_planned_task_rel_planned_task.csv</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>u_u_predecessor_correlation_id</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>planned_task_rel_planned_task</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Reference (scripted)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>answer = new SPMMigrationUtil().byCorrelation(..., source.u_u_predecessor_correlation_id)</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>out-of-box</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>docs/05 section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>u_imp_spm_dependency</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>04_planned_task_rel_planned_task.csv</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>u_u_successor_correlation_id</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>planned_task_rel_planned_task</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Reference (scripted)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>answer = new SPMMigrationUtil().byCorrelation(..., source.u_u_successor_correlation_id)</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>out-of-box</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>docs/05 section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>u_imp_spm_dependency</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>04_planned_task_rel_planned_task.csv</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>u_type</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>planned_task_rel_planned_task</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Values from value map 'dependency_type' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>u_imp_spm_dependency</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>04_planned_task_rel_planned_task.csv</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>u_lag</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>planned_task_rel_planned_task</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>lag</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>u_u_project_correlation_id</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Reference (scripted)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>answer = new SPMMigrationUtil().byCorrelation(..., source.u_u_project_correlation_id)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>out-of-box</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>docs/05 section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>u_as_on</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>as_on</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Date format yyyy-MM-dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>u_overall_health</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>overall_health</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Values from value map 'health' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>u_schedule</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Values from value map 'health' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>u_cost</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Values from value map 'health' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>u_resources</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Values from value map 'health' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>u_scope</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Values from value map 'health' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>u_u_risk_health</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>u_risk_health</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>PROPOSED - create before load</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Values from value map 'health' - must be stored values</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>u_imp_spm_status</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>05_project_status.csv</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>u_comments</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>project_status</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>String / text</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>out-of-box - verify with validate-fields</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L107"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -12025,7 +17431,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>All Asana (HR) demands. Demand list stored values from Demand_Form_Fields</t>
+          <t>All Asana (HR) demands -&gt; Human Resources on the demand list</t>
         </is>
       </c>
     </row>
@@ -12037,22 +17443,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>asana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Construction/Relocation</t>
+          <t>BSMH</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Construction Renovation Relocation</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Demand list differs from project list (decision D1)</t>
+          <t>Entity/Organization is not a demand category - HR demands stay Human Resources</t>
         </is>
       </c>
     </row>
@@ -12064,22 +17470,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>asana</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Onboarding (new Provider group - no construction)</t>
+          <t>RSFH</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Employed Physician Onboarding</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Closest match - CONFIRM</t>
+          <t>Entity/Organization is not a demand category - HR demands stay Human Resources</t>
         </is>
       </c>
     </row>
@@ -12091,20 +17497,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>asana</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>GBS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EHR</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Entity/Organization is not a demand category - HR demands stay Human Resources</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -12114,20 +17524,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>asana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>External Partners</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Entity/Organization is not a demand category - HR demands stay Human Resources</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -12142,15 +17556,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Revenue Cycle (includes Ensemble requests</t>
+          <t>Construction/Relocation</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Rev Cycle</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>Construction Renovation Relocation</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Demand list differs from project list (decision D1)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -12165,15 +17583,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Revenue Cycle (includes Ensemble requests)</t>
+          <t>Onboarding (new Provider group - no construction)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Rev Cycle</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>Employed Physician Onboarding</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Closest match - CONFIRM</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12188,12 +17610,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>EHR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -12201,76 +17623,68 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>business_category_demand</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>adaptive</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>u_sites list; transform script resolves names to sys_ids. Region values not supplied - extend once exported</t>
-        </is>
-      </c>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>business_category_demand</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>adaptive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>Revenue Cycle (includes Ensemble requests</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Market codes used in Project Funding Type</t>
-        </is>
-      </c>
+          <t>Rev Cycle</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>business_category_demand</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>adaptive</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Revenue Cycle (includes Ensemble requests)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Rev Cycle</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -12278,22 +17692,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>business_category_demand</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>adaptive</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GVL</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Greenville</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -12311,15 +17725,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hampton Roads</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Hampton Roads</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>u_sites list; transform script resolves names to sys_ids. Region values not supplied - extend once exported</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -12334,15 +17752,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HMP</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Hampton Roads</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Market codes used in Project Funding Type</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -12357,12 +17779,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -12380,12 +17802,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>GVL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Greenville</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -12403,12 +17825,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lorain</t>
+          <t>Hampton Roads</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Lorain</t>
+          <t>Hampton Roads</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -12426,12 +17848,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LOR</t>
+          <t>HMP</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lorain</t>
+          <t>Hampton Roads</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -12449,12 +17871,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -12472,12 +17894,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -12495,12 +17917,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>Lorain</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>Lorain</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -12518,12 +17940,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>LOR</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>Lorain</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -12541,12 +17963,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -12564,12 +17986,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -12587,12 +18009,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Youngstown</t>
+          <t>Springfield</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Youngstown</t>
+          <t>Springfield</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -12610,12 +18032,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>YNG</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Youngstown</t>
+          <t>Springfield</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -12633,12 +18055,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Home Office</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Home Office</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -12656,12 +18078,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RSFH</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Roper St. Francis Healthcare</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -12679,12 +18101,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Roper St Francis</t>
+          <t>Youngstown</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Roper St. Francis Healthcare</t>
+          <t>Youngstown</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -12702,12 +18124,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>YNG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Youngstown</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -12725,12 +18147,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Home Office</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Home Office</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -12748,19 +18170,15 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Paducah</t>
+          <t>RSFH</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>ASSUMPTION - Paducah is not on the Sites list (DQ14). CONFIRM</t>
-        </is>
-      </c>
+          <t>Roper St. Francis Healthcare</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12775,24 +18193,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PAD</t>
+          <t>Roper St Francis</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>ASSUMPTION - CONFIRM</t>
-        </is>
-      </c>
+          <t>Roper St. Francis Healthcare</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>business_unit</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12802,24 +18216,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BSMH</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>BSMH</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Entity/Organization + Customers -&gt; business_unit (name must match business_unit.name). CONFIRM names</t>
-        </is>
-      </c>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>business_unit</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12829,12 +18239,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RSFH</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>RSFH</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -12842,7 +18252,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>business_unit</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12852,20 +18262,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GBS</t>
+          <t>Paducah</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GBS</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ASSUMPTION - Paducah is not on the Sites list (DQ14). CONFIRM</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>business_unit</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12875,24 +18289,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>External Partners</t>
+          <t>PAD</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>External Partners</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>May not warrant a business unit - decision D8</t>
+          <t>ASSUMPTION - CONFIRM</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>tshirt_size</t>
+          <t>business_unit</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12902,24 +18316,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>BSMH</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>BSMH</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Size/Complexity -&gt; demand T-Shirt Size. CONFIRM stored values</t>
+          <t>Entity/Organization + Customers -&gt; business_unit (name must match business_unit.name). CONFIRM names</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>tshirt_size</t>
+          <t>business_unit</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12929,12 +18343,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>RSFH</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>RSFH</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -12942,7 +18356,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>tshirt_size</t>
+          <t>business_unit</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12952,12 +18366,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>GBS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>GBS</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -12965,72 +18379,76 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>estimate_type</t>
+          <t>business_unit</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Detailed Estimate</t>
+          <t>External Partners</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>detailed_estimate</t>
+          <t>External Partners</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Proposed new choice field u_estimate_type (we define the values)</t>
+          <t>May not warrant a business unit - decision D8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>estimate_type</t>
+          <t>tshirt_size</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SAT - Detailed Estimate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>sat_detailed_estimate</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Size/Complexity -&gt; demand T-Shirt Size. CONFIRM stored values</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>estimate_type</t>
+          <t>tshirt_size</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Detailed Estimate- Straight to PM</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>detailed_estimate_straight_to_pm</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -13038,129 +18456,125 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>estimate_type</t>
+          <t>tshirt_size</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>packaging</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Only on the Picklists sheet - confirm it is in use</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>program_name</t>
+          <t>estimate_type</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>asana</t>
+          <t>adaptive</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ireland Projects 2026 - 2027</t>
+          <t>Detailed Estimate</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ireland Projects 2026 - 2027</t>
+          <t>detailed_estimate</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Asana sections -&gt; pm_program.name (decision D2). Other sections pass through unchanged</t>
+          <t>Proposed new choice field u_estimate_type (we define the values)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>portfolio_name</t>
+          <t>estimate_type</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>asana</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>adaptive</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SAT - Detailed Estimate</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Human Resources</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>ASSUMPTION: every Asana item belongs to one HR portfolio (decision D2)</t>
-        </is>
-      </c>
+          <t>sat_detailed_estimate</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>estimate_type</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>adaptive</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Detailed Estimate- Straight to PM</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>1 - Critical (task.priority) - neither source has priority today</t>
-        </is>
-      </c>
+          <t>detailed_estimate_straight_to_pm</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>estimate_type</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>adaptive</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>packaging</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Only on the Picklists sheet - confirm it is in use</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13175,15 +18589,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1 - Critical (task.priority) - neither source has priority today</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13198,12 +18616,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -13211,7 +18629,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>dependency_type</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13221,39 +18639,35 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>fs</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Finish to Start</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>dependency_type</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Finish to Start</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -13266,20 +18680,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>adaptive</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Start to Start</t>
+          <t>fs</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>fs</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Finish to Start</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13294,12 +18712,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Finish to Finish</t>
+          <t>Finish to Start</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ff</t>
+          <t>fs</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -13317,12 +18735,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Start to Finish</t>
+          <t>Start to Start</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>sf</t>
+          <t>ss</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -13330,24 +18748,174 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>dependency_type</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>adaptive</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Finish to Finish</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ff</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>dependency_type</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>adaptive</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Start to Finish</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>sf</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
           <t>project_phase</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
         <is>
           <t>Adaptive Phase passes through; map once SN phase choices are confirmed (decision D5)</t>
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>business_category_project</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>asana</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>RSFH</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>rsfh</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Entity/Organization -&gt; parent.u_business_category (Asana task mapping). 'BSMH, RSFH' -&gt; rsfh (first mappable value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>portfolio_name</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>asana</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Benefits</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Benefits &amp; Well-Being</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Task COE -&gt; parent.portfolio; COE values aligned to section (portfolio) names. CONFIRM pm_portfolio names</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>portfolio_name</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>asana</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Culture &amp; Learning</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>portfolio_name</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>asana</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Compensation</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Compensation</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Other sections/COEs pass through unchanged and must match pm_portfolio.name</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E133"/>
+  <autoFilter ref="A1:E139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/mapping/mapping_workbook.xlsx
+++ b/mapping/mapping_workbook.xlsx
@@ -562,7 +562,7 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>(a) new u_cost_center reference to cmn_cost_center (b) department</t>
+          <t>(a) implementation team provides u_cost_center (reference to cmn_cost_center) (b) map to department</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>(a) if Finance reports by cost center; else (b)</t>
+          <t>Ask the implementation team whether u_cost_center will exist; if not, load to department (if departments carry cost centers) or keep it in the description</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finance + implementation team</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>(a) 7 custom fields on pm_project (and the intake ones on dmn_demand) (b) append to description (c) create a linked Completed demand holding intake dates</t>
+          <t>(a) implementation team provides the 7 fields on pm_project (b) keep them in the description block</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>(a) - these drive leadership and cycle-time reporting. Built into target_mapping as u_ fields</t>
+          <t>(a) if the implementation team agrees - these drive leadership and cycle-time reporting. The load files already carry the columns; they are dropped if the fields do not exist</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Nordic PMO</t>
+          <t>Nordic PMO + implementation team</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>(a) add u_risk_health to project_status (b) drop</t>
+          <t>(a) implementation team provides u_risk_health on project_status (b) drop</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>(a) - one field; keeps the 6-indicator status view</t>
+          <t>(a) if the implementation team agrees; otherwise the Risk RAG is dropped</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>PMO</t>
+          <t>PMO + implementation team</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="38" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="47" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -10553,7 +10553,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -10600,7 +10600,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -11955,7 +11955,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
@@ -12002,7 +12002,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
@@ -13392,7 +13392,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
@@ -13439,7 +13439,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
@@ -14836,7 +14836,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr"/>
@@ -14883,7 +14883,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
@@ -16332,7 +16332,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr"/>
@@ -16379,7 +16379,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr"/>
@@ -17612,7 +17612,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -17824,7 +17824,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -17875,7 +17875,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -17926,7 +17926,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -17977,7 +17977,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -18028,7 +18028,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -18079,7 +18079,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -18334,7 +18334,7 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr"/>
@@ -19798,7 +19798,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED - create before load</t>
+          <t>custom - confirm exists (implementation team)</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
